--- a/02_加值成品/生物/生物6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-3 基因、突變與生物技術　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物6-3 基因、突變與生物技術　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>決定性狀的遺傳單位是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>突變</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>變異</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>基因</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>基因位於什麼上？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>提供變異素材</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>變異</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>染色體</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>DNA</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>核內</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>基因由什麼組成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>提供變異素材</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>DNA</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>生物技術</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>分子</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>DNA訊息改變稱？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>突變</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>子代</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>變異</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>改變</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>突變是什麼的來源？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>性狀</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>變異</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>多樣</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>基因改造屬於？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>生物技術</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>倫理</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>性狀</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>無影響</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>技術</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>突變一定有害嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>增產抗蟲等</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>不一定</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>子代</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>中性/有利</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>親子鑑定利用？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>變異</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>突變</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>DNA</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>遺傳物質</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>DNA存在於細胞的哪個構造？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>細胞核(染色體上)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>基因工程生產藥物如胰島素</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>可能無影響甚至有利於適應</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>DNA組成基因基因位於染色體上</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>核</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>遺傳訊息由親代傳給？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>提供變異素材</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>子代</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>農業與醫學</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>遺傳</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-3 基因、突變與生物技術　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物6-3 基因、突變與生物技術　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>突變可能是有利、有害或？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>突變</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>生物技術</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>無影響</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>基因工程</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>生物技術可應用於？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>農業與醫學</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>細胞核染色體</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>提供變異素材</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>用細菌生產胰島素屬？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>基因工程</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>突變</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>增產抗蟲等</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>技術</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>基改作物的目的常是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>子代</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>增產抗蟲等</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>生物技術</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>改良</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>基因位於細胞的？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>細胞核染色體</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>基因工程</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>倫理</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>突變</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>核</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>複製技術能產生？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>基因相同的個體</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>可增產抗病但引環境與倫理疑慮</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>細胞核(染色體上)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>決定性狀並傳給後代</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>複製</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>突變對演化的意義？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>提供變異素材</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>細胞核染色體</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>生物技術</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>變異</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>演化</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>生物技術也帶來什麼議題？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>倫理</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>生物技術</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>無影響</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>討論</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>輻射與化學物質可能誘發？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>提供變異素材</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>子代</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>農業與醫學</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>突變</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>誘變</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>基因決定生物的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>性狀</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>突變</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DNA</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>倫理</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>性狀</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-3 基因、突變與生物技術　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物6-3 基因、突變與生物技術　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明基因、DNA、染色體三者關係？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>DNA組成基因基因位於染色體上</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>產生變異供天擇作用</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>決定性狀並傳給後代</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>善用其利並謹慎評估風險倫理</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>關係</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何突變不一定有害？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>可增產抗病但引環境與倫理疑慮</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>環境與食品安全等倫理考量</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>DNA組成基因基因位於染色體上</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>可能無影響甚至有利於適應</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>分析基改作物的利與弊？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>基因工程生產藥物如胰島素</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>發生在生殖細胞</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>可增產抗病但引環境與倫理疑慮</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>可能無影響甚至有利於適應</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>利弊</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>突變如何成為演化的原料？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>發生在生殖細胞</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>細胞核(染色體上)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>環境與食品安全等倫理考量</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>產生變異供天擇作用</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>原料</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>生物技術在醫學的應用舉例？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>基因工程生產藥物如胰島素</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>基因相同的個體</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>發生在生殖細胞</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>生命價值與應用界線</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>醫學</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>複製技術可能引發哪些倫理討論？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>可能無影響甚至有利於適應</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>基因工程生產藥物如胰島素</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>生命價值與應用界線</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>可增產抗病但引環境與倫理疑慮</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>倫理</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>DNA攜帶遺傳訊息的意義？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>基因工程生產藥物如胰島素</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>基因相同的個體</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>決定性狀並傳給後代</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>可增產抗病但引環境與倫理疑慮</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>訊息</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>如何理性看待生物技術發展？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>善用其利並謹慎評估風險倫理</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>生命價值與應用界線</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>基因相同的個體</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>產生變異供天擇作用</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>態度</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何有些突變能遺傳給後代？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>生命價值與應用界線</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>產生變異供天擇作用</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>發生在生殖細胞</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>基因工程生產藥物如胰島素</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>遺傳</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>基因改造食品引發疑慮的原因？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>發生在生殖細胞</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>環境與食品安全等倫理考量</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>基因工程生產藥物如胰島素</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>決定性狀並傳給後代</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>倫理</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>遺傳單位：基因是控制身高、膚色等各種性狀的最小遺傳單位</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>核內</t>
+          <t>位於染色體：基因就排列在細胞核裡的染色體上,一條染色體上有很多個基因</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>分子</t>
+          <t>DNA組成：基因其實是一段一段的DNA分子,DNA上記錄著遺傳訊息</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>改變</t>
+          <t>突變：DNA上的遺傳訊息發生變化,這種改變就叫做突變</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>多樣</t>
+          <t>變異來源：突變會讓生物出現和原本不同的性狀,是生物產生變異的來源之一</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>技術</t>
+          <t>生物技術：利用基因原理去改造生物的方法,就屬於生物技術的一種</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>中性/有利</t>
+          <t>不一定有害：突變可能對生物有害、有利,也可能完全沒有影響,不是每次都有害</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>遺傳物質</t>
+          <t>利用DNA：每個人的DNA都不同,親子鑑定就是比對DNA來確認親屬關係</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>核</t>
+          <t>核：DNA主要存在於細胞核內，纏繞成染色體的形式儲存遺傳訊息</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>遺傳</t>
+          <t>遺傳：親代透過生殖過程把DNA所攜帶的遺傳訊息傳遞給下一代的子代</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>三種可能：突變發生後,對生物的影響可能是有害、有利,也可能完全沒有影響</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>農業與醫學：生物技術常被用來改良農作物,或是用在醫學上生產藥物治病</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>技術</t>
+          <t>基因工程：把人類的基因放進細菌裡讓它生產胰島素,這種技術叫基因工程</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>改良</t>
+          <t>增產抗蟲：改造作物的基因常是為了讓農作物產量更多或更能抵抗病蟲害</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>核</t>
+          <t>細胞核染色體：基因位在細胞核內的染色體上,不會出現在細胞質中</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>複製</t>
+          <t>基因相同：複製技術可以製造出和原本個體基因完全一樣的另一個生物</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>演化</t>
+          <t>提供變異素材：突變會產生新的性狀,這些變異正是生物演化能發生的原始材料</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>討論</t>
+          <t>倫理議題：生物技術雖然方便,但也引發像複製人這類該不該做的倫理討論</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>誘變</t>
+          <t>誘變：某些輻射線或化學物質會破壞DNA的結構，使基因發生突變</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>性狀</t>
+          <t>性狀：基因所攜帶的訊息，決定了生物表現出來的各種性狀，例如外觀、生理特徵等</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>關係</t>
+          <t>層層關係：DNA組成基因,許多基因排列在染色體上,三者是由小到大的組成關係</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>未必有害：突變只是DNA訊息改變,結果可能沒有影響,甚至讓生物更適應環境</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>利弊</t>
+          <t>利弊並存：基改作物能增產又抗病蟲害,但也可能影響生態環境並引發倫理爭議</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>原料</t>
+          <t>演化原料：突變製造出不同的性狀,這些變異讓天擇有材料可以挑選,推動演化</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>醫學</t>
+          <t>醫學應用：例如利用基因工程讓細菌生產胰島素,用來治療糖尿病患者</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>倫理</t>
+          <t>倫理討論：複製技術牽涉到生命該不該被複製、應用的界線在哪裡等爭議</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>訊息</t>
+          <t>傳遞訊息：DNA上記錄的遺傳訊息會決定生物的性狀,並透過生殖傳給下一代</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>態度</t>
+          <t>理性看待：應該善用生物技術帶來的好處,同時謹慎評估可能的風險與倫理問題</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>遺傳</t>
+          <t>遺傳：如果突變發生在精子或卵這類生殖細胞裡，這個改變過的基因就有機會隨著受精傳遞給下一代;若突變只發生在體細胞，則不會遺傳給後代</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>倫理</t>
+          <t>倫理：基因改造技術牽涉到對生態環境的長期影響、食品安全性評估，以及是否符合社會倫理等多方面考量，因此常引發討論與疑慮</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-3_三種難度測驗卷.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>染色體</t>
+          <t>農業與醫學</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>突變</t>
+          <t>增產抗蟲等</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>提供變異素材</t>
+          <t>子代</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>變異</t>
+          <t>倫理</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>DNA</t>
+          <t>生物技術</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>基因</t>
+          <t>子代</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>性狀</t>
+          <t>生物技術</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>染色體</t>
+          <t>DNA</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>DNA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>突變</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>增產抗蟲等</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>不一定</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>基因工程</t>
+          <t>生物技術</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>倫理</t>
+          <t>突變</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>突變</t>
+          <t>基因</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>細胞核染色體</t>
+          <t>DNA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>生物技術</t>
+          <t>子代</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>變異</t>
+          <t>農業與醫學</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
